--- a/public/files/headcount.xlsx
+++ b/public/files/headcount.xlsx
@@ -131,6 +131,40 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>45847.78735596065</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>45847.78735596065</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>